--- a/sheets/민요/검수/신고산 타령-2.xlsx
+++ b/sheets/민요/검수/신고산 타령-2.xlsx
@@ -31,7 +31,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">신고산 타령</t>
@@ -62,7 +62,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">파일</t>
@@ -81,7 +81,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">민요</t>
@@ -98,7 +98,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">신고산 타령</t>
@@ -133,7 +133,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자 </t>
@@ -152,7 +152,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">행수</t>
@@ -171,7 +171,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -191,7 +191,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">비고</t>
@@ -210,7 +210,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">노란 칸</t>
@@ -234,7 +234,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">팔레트 외 글자</t>
@@ -253,7 +253,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">주황 칸</t>
@@ -294,7 +294,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">민요채보</t>
@@ -311,7 +311,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">궁초댕기 신고산 타령</t>
@@ -330,7 +330,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장에 두 곡</t>
@@ -347,7 +347,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">오른쪽 </t>
@@ -364,7 +364,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">신고산 타령 </t>
@@ -381,7 +381,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">키</t>
@@ -398,7 +398,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -415,7 +415,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -432,7 +432,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">빈 줄</t>
@@ -449,7 +449,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">왼쪽 </t>
@@ -466,7 +466,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">궁초댕기 </t>
@@ -483,7 +483,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">키</t>
@@ -500,7 +500,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -517,7 +517,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -534,7 +534,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">빈 줄</t>
@@ -551,7 +551,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">맨 위 여백에 장단 표기 있음</t>
@@ -568,7 +568,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">부제</t>
@@ -585,7 +585,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -602,7 +602,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">칸마다 가로선</t>
@@ -619,7 +619,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">굵은 선 </t>
@@ -636,7 +636,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">칸마다</t>
@@ -653,7 +653,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">각 율명 줄 오른쪽에 가사 칸</t>
@@ -670,7 +670,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사 칸의 </t>
@@ -687,7 +687,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">표시는 경계 바로 위 정간 율명 끝에 ‹로 적음</t>
@@ -704,7 +704,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -721,7 +721,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">맨 왼쪽</t>
@@ -738,7 +738,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">은 용지를 거꾸로 돌려 적은 가락이라 </t>
@@ -755,7 +755,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">돌려 읽은 순서로 정간 번호를 매김</t>
@@ -772,7 +772,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -789,7 +789,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">용지 아래쪽</t>
@@ -806,7 +806,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사는 바깥 왼쪽 여백에 거꾸로 적힘</t>
@@ -823,7 +823,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">신고산 타령 다른 절로 보임</t>
@@ -840,7 +840,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">재판독 초안</t>
@@ -865,7 +865,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">원본처럼 오른쪽이 </t>
@@ -882,7 +882,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -899,7 +899,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">악보 시트도 같은 배치</t>
@@ -916,7 +916,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">여러 페이지는 악보 시트 아래쪽으로 이어짐</t>
@@ -933,7 +933,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">빈 행 </t>
@@ -950,7 +950,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">개</t>
@@ -967,7 +967,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">인쇄 시 페이지마다 새 종이</t>
@@ -984,7 +984,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄은 항상 맨 오른쪽 두 열</t>
@@ -1001,7 +1001,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -1018,7 +1018,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사</t>
@@ -1035,7 +1035,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
@@ -1052,7 +1052,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -1069,7 +1069,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
@@ -1086,7 +1086,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간마다 가사 칸 가로선을 묶음</t>
@@ -1103,7 +1103,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명 글자는 가사의 두 배</t>
@@ -1120,7 +1120,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">인쇄는 </t>
@@ -1137,7 +1137,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">세로</t>
@@ -1154,7 +1154,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">원본 한 페이지 </t>
@@ -1171,7 +1171,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">종이 한 장</t>
@@ -1188,7 +1188,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 번호 열</t>
@@ -1205,7 +1205,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">머리 행 없음 — 제목 행 아래 </t>
@@ -1222,7 +1222,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">번째 행이 정간 </t>
@@ -1239,7 +1239,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">이므로 행을 지우거나 끼워 넣지 말고</t>
@@ -1256,7 +1256,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">제목 병합도 풀지 말 것</t>
@@ -1273,7 +1273,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장이 </t>
@@ -1290,7 +1290,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄을 넘으면 </t>
@@ -1307,7 +1307,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄씩 다음 페이지</t>
@@ -1320,7 +1320,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 안에서 위→아래 순서</t>
@@ -1337,7 +1337,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">칸 안 줄바꿈으로 구분 </t>
@@ -1354,7 +1354,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">앱과 같음</t>
@@ -1376,7 +1376,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">– 연음 </t>
@@ -1393,7 +1393,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">쉼 </t>
@@ -1410,7 +1410,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">점 </t>
@@ -1427,7 +1427,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">동그라미 </t>
@@ -1444,7 +1444,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">두 점 </t>
@@ -1461,7 +1461,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 경계 표시 </t>
@@ -1478,7 +1478,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">／ 사선 </t>
@@ -1495,7 +1495,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">／ 는 화면 표시 전용</t>
@@ -1523,7 +1523,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -1540,7 +1540,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">기호표에 없는 글자 </t>
@@ -1557,7 +1557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">포함</t>
@@ -1574,7 +1574,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">반드시 수정</t>
@@ -1587,7 +1587,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">악보 시트를 고쳐 </t>
@@ -1604,7 +1604,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">로 저장한 뒤 </t>
@@ -1621,7 +1621,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">작업</t>
@@ -1638,7 +1638,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">실행 → </t>
@@ -1655,7 +1655,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">반영</t>
@@ -1672,7 +1672,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정보</t>
@@ -1689,7 +1689,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간목록 시트는 반영 안 됨</t>
@@ -1712,7 +1712,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -1731,7 +1731,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">판독</t>
@@ -1752,7 +1752,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -1771,7 +1771,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">앱</t>
@@ -1800,7 +1800,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -1817,7 +1817,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -1834,7 +1834,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -1858,7 +1858,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -1875,7 +1875,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -1892,7 +1892,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -1916,7 +1916,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -1933,7 +1933,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -1950,7 +1950,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -1971,7 +1971,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -1988,7 +1988,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2015,7 +2015,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌汰</t>
@@ -2032,7 +2032,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2059,7 +2059,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2076,7 +2076,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2093,7 +2093,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2111,7 +2111,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無南</t>
@@ -2128,7 +2128,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲</t>
@@ -2161,7 +2161,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2178,7 +2178,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2196,7 +2196,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2213,7 +2213,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2230,7 +2230,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲</t>
@@ -2248,7 +2248,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2265,7 +2265,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2285,7 +2285,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2302,7 +2302,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2329,7 +2329,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2346,7 +2346,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2364,7 +2364,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">아래 글자 古</t>
@@ -2381,7 +2381,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">氵古</t>
@@ -2415,7 +2415,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2432,7 +2432,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2449,7 +2449,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2467,7 +2467,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2484,7 +2484,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2501,7 +2501,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -2522,7 +2522,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌汰</t>
@@ -2539,7 +2539,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2559,7 +2559,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -2576,7 +2576,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -2603,7 +2603,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -2620,7 +2620,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2650,7 +2650,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -2667,7 +2667,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2687,7 +2687,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞
@@ -2701,7 +2701,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2718,7 +2718,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2748,7 +2748,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2765,7 +2765,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2785,7 +2785,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌
@@ -2799,7 +2799,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2816,7 +2816,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2834,7 +2834,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲南</t>
@@ -2875,7 +2875,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -2892,7 +2892,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -2928,7 +2928,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2945,7 +2945,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2972,7 +2972,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌汰</t>
@@ -2989,7 +2989,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌汰</t>
@@ -3006,7 +3006,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無南</t>
@@ -3023,7 +3023,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲</t>
@@ -3040,7 +3040,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲</t>
@@ -3057,7 +3057,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -3075,7 +3075,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3092,7 +3092,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -3109,7 +3109,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3133,7 +3133,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -3150,7 +3150,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3167,7 +3167,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -3184,7 +3184,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
@@ -3223,7 +3223,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3240,7 +3240,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -3261,7 +3261,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -3278,7 +3278,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3296,7 +3296,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사 서</t>
@@ -3313,7 +3313,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">어</t>
@@ -3335,7 +3335,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사 러</t>
@@ -3352,7 +3352,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">어</t>
@@ -3371,7 +3371,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲</t>
@@ -3388,7 +3388,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑</t>
@@ -3470,31 +3470,31 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
@@ -3513,17 +3513,22 @@
     <font>
       <b val="true"/>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3617,7 +3622,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3691,6 +3696,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7126,520 +7175,520 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="20" width="5.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="13" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="S3" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="T3" s="13" t="s">
+      <c r="T3" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="14" t="s">
+      <c r="U3" s="25" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="13" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="S4" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="U4" s="16"/>
+      <c r="U4" s="27"/>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="13" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="S5" s="16" t="s">
+      <c r="S5" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="T5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="U5" s="16"/>
+      <c r="U5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="13" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="S6" s="17" t="s">
+      <c r="S6" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="T6" s="13" t="s">
+      <c r="T6" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="U6" s="17"/>
+      <c r="U6" s="28"/>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="11" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="T7" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="U7" s="12" t="s">
+      <c r="U7" s="23" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="13" t="s">
+      <c r="B8" s="24"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="S8" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="T8" s="13" t="s">
+      <c r="T8" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="16" t="s">
+      <c r="U8" s="27" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="13" t="s">
+      <c r="B9" s="22"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="S9" s="16" t="s">
+      <c r="S9" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="T9" s="13" t="s">
+      <c r="T9" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="U9" s="16" t="s">
+      <c r="U9" s="27" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="13" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="S10" s="17" t="s">
+      <c r="S10" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="T10" s="13" t="s">
+      <c r="T10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="U10" s="17" t="s">
+      <c r="U10" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="13" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="S11" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T11" s="13" t="s">
+      <c r="T11" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="U11" s="14" t="s">
+      <c r="U11" s="25" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="13" t="s">
+      <c r="B12" s="24"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="S12" s="16" t="s">
+      <c r="S12" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="T12" s="13" t="s">
+      <c r="T12" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="U12" s="16" t="s">
+      <c r="U12" s="27" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="13" t="s">
+      <c r="B13" s="22"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="S13" s="16" t="s">
+      <c r="S13" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="T13" s="13" t="s">
+      <c r="T13" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="U13" s="16" t="s">
+      <c r="U13" s="27" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="13" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="S14" s="17" t="s">
+      <c r="S14" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="T14" s="13" t="s">
+      <c r="T14" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="U14" s="17" t="s">
+      <c r="U14" s="28" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="13" t="s">
+      <c r="B15" s="24"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="S15" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="T15" s="13" t="s">
+      <c r="T15" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="U15" s="14" t="s">
+      <c r="U15" s="25" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="13" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="S16" s="16" t="s">
+      <c r="S16" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="T16" s="13" t="s">
+      <c r="T16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="U16" s="16" t="s">
+      <c r="U16" s="27" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="13" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="S17" s="16"/>
-      <c r="T17" s="13" t="s">
+      <c r="S17" s="27"/>
+      <c r="T17" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="U17" s="16" t="s">
+      <c r="U17" s="27" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="13" t="s">
+      <c r="B18" s="24"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="S18" s="17"/>
-      <c r="T18" s="13" t="s">
+      <c r="S18" s="28"/>
+      <c r="T18" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="U18" s="17" t="s">
+      <c r="U18" s="28" t="s">
         <v>204</v>
       </c>
     </row>

--- a/sheets/민요/검수/신고산 타령-2.xlsx
+++ b/sheets/민요/검수/신고산 타령-2.xlsx
@@ -512,10 +512,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/신고산 타령-2.xlsx
+++ b/sheets/민요/검수/신고산 타령-2.xlsx
@@ -458,17 +458,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -585,7 +585,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -639,6 +639,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2093,238 +2133,238 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:E18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="83.33" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B4" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B5" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B7" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="22" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B8" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B9" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B10" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B11" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="18" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B12" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B13" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B14" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B15" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="18" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="19" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B17" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="19" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.16" customHeight="true">
+      <c r="B18" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="23"/>
+      <c r="D18" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="20" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2334,7 +2374,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/신고산 타령-2.xlsx
+++ b/sheets/민요/검수/신고산 타령-2.xlsx
@@ -2139,9 +2139,9 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
   </cols>
   <sheetData>
